--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251103_201957.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251103_201957.xlsx
@@ -4370,7 +4370,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251103_201957.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251103_201957.xlsx
@@ -4370,7 +4370,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251103_201957.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251103_201957.xlsx
@@ -5186,7 +5186,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251103_201957.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251103_201957.xlsx
@@ -7148,7 +7148,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251103_201957.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251103_201957.xlsx
@@ -7148,7 +7148,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251103_201957.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251103_201957.xlsx
@@ -4370,7 +4370,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251103_201957.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251103_201957.xlsx
@@ -4370,7 +4370,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251103_201957.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251103_201957.xlsx
@@ -4370,7 +4370,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251103_201957.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251103_201957.xlsx
@@ -4370,7 +4370,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251103_201957.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251103_201957.xlsx
@@ -4370,7 +4370,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251103_201957.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251103_201957.xlsx
@@ -4370,7 +4370,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251103_201957.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251103_201957.xlsx
@@ -4370,7 +4370,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
